--- a/apps/web/public/templates/scopewise-mitre-environment.xlsx
+++ b/apps/web/public/templates/scopewise-mitre-environment.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log Sources" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Tooling" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crown Jewels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log Sources" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Tooling" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crown Jewels" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +31,17 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,9 +64,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,51 +441,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Linux</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Azure AD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Microsoft 365</t>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ScopeWise MITRE Environment Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="8" customHeight="1">
+      <c r="A2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>This workbook is optional. Uploading it lets ScopeWise filter out techniques that don't apply to your environment and prioritize gaps by what you could realistically detect first. Skipping it still produces a coverage assessment -- just a conservative lower bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="8" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Sheets in this workbook (all optional -- a missing sheet is noted as an assumption, never an error):</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1">
+      <c r="A6" s="3" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Assets -- your platform/technology inventory (e.g. Windows, AWS, Azure AD). Used to mark techniques that don't apply to any platform you have (e.g. macOS-only techniques when you have no Mac fleet) as Not Applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Log Sources -- telemetry you already collect (e.g. Sysmon, CloudTrail). Used to prioritize gaps you could detect right now with data you already have. Optional health columns (Parser / Format, Normalized (Y/N), Last Event Seen) sharpen that prioritization -- a source that isn't normalized or hasn't seen recent events is treated as needing attention before you rely on it, not as fully ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Security Tooling -- products you own but may not have onboarded for logging yet. Used for the next-tier "onboard this, then detect" gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Crown Jewels -- free text describing your most critical assets (e.g. "customer database", "payment gateway"). Used only to nudge the order gaps are shown in when they're relevant to what you described -- it never changes a coverage percentage or a technique's status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1">
+      <c r="A11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Honesty note: ScopeWise never ingests raw logs and never verifies a specific field is present in your data. Everything here is metadata you tell us about your environment -- if something looks off, it's worth double-checking your own inventory, not just trusting this workbook.</t>
         </is>
       </c>
     </row>
@@ -479,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -488,28 +535,42 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Platform</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sysmon</t>
+          <t>Windows</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Windows Event Logs</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CloudTrail</t>
+          <t>Azure AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Microsoft 365</t>
         </is>
       </c>
     </row>
@@ -524,30 +585,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Present?</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Parser / Format</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Normalized (Y/N)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Last Event Seen</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CrowdStrike Falcon EDR</t>
+          <t>Sysmon</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sysmon XML</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Proofpoint Email Security</t>
+          <t>Windows Event Logs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CloudTrail</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CloudTrail JSON</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
         </is>
       </c>
     </row>
@@ -571,6 +708,44 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CrowdStrike Falcon EDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Proofpoint Email Security</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Asset</t>
         </is>
       </c>

--- a/apps/web/public/templates/scopewise-mitre-environment.xlsx
+++ b/apps/web/public/templates/scopewise-mitre-environment.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -494,22 +494,29 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Security Tooling -- products you own but may not have onboarded for logging yet. Used for the next-tier "onboard this, then detect" gaps.</t>
+          <t>Tip: if one device sends more than one kind of log, list each log type as its own row in Log Sources -- e.g. "Infoblox - DNS logs" and "Infoblox - SSH logs" -- so each stream gets credited separately.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Security Tooling -- products you own but may not have onboarded for logging yet. Used for the next-tier "onboard this, then detect" gaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
           <t>Crown Jewels -- free text describing your most critical assets (e.g. "customer database", "payment gateway"). Used only to nudge the order gaps are shown in when they're relevant to what you described -- it never changes a coverage percentage or a technique's status.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="3" t="n"/>
-    </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Honesty note: ScopeWise never ingests raw logs and never verifies a specific field is present in your data. Everything here is metadata you tell us about your environment -- if something looks off, it's worth double-checking your own inventory, not just trusting this workbook.</t>
         </is>

--- a/apps/web/public/templates/scopewise-mitre-environment.xlsx
+++ b/apps/web/public/templates/scopewise-mitre-environment.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,28 +31,37 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
     <font>
-      <sz val="11"/>
-    </font>
-    <font>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000057B8"/>
+        <bgColor rgb="000057B8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,22 +69,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="008496AD"/>
+      </left>
+      <right style="thin">
+        <color rgb="008496AD"/>
+      </right>
+      <top style="thin">
+        <color rgb="008496AD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="008496AD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,75 +477,75 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ScopeWise MITRE Environment Workbook</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="3" t="n"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>This workbook is optional. Uploading it lets ScopeWise filter out techniques that don't apply to your environment and prioritize gaps by what you could realistically detect first. Skipping it still produces a coverage assessment -- just a conservative lower bound.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="8" customHeight="1">
-      <c r="A4" s="3" t="n"/>
+      <c r="A4" s="2" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Sheets in this workbook (all optional -- a missing sheet is noted as an assumption, never an error):</t>
         </is>
       </c>
     </row>
     <row r="6" ht="8" customHeight="1">
-      <c r="A6" s="3" t="n"/>
+      <c r="A6" s="2" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Assets -- your platform/technology inventory (e.g. Windows, AWS, Azure AD). Used to mark techniques that don't apply to any platform you have (e.g. macOS-only techniques when you have no Mac fleet) as Not Applicable.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Log Sources -- telemetry you already collect (e.g. Sysmon, CloudTrail). Used to prioritize gaps you could detect right now with data you already have. Optional health columns (Parser / Format, Normalized (Y/N), Last Event Seen) sharpen that prioritization -- a source that isn't normalized or hasn't seen recent events is treated as needing attention before you rely on it, not as fully ready.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Tip: if one device sends more than one kind of log, list each log type as its own row in Log Sources -- e.g. "Infoblox - DNS logs" and "Infoblox - SSH logs" -- so each stream gets credited separately.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Security Tooling -- products you own but may not have onboarded for logging yet. Used for the next-tier "onboard this, then detect" gaps.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Crown Jewels -- free text describing your most critical assets (e.g. "customer database", "payment gateway"). Used only to nudge the order gaps are shown in when they're relevant to what you described -- it never changes a coverage percentage or a technique's status.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Honesty note: ScopeWise never ingests raw logs and never verifies a specific field is present in your data. Everything here is metadata you tell us about your environment -- if something looks off, it's worth double-checking your own inventory, not just trusting this workbook.</t>
         </is>
@@ -533,53 +562,353 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Windows</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Linux</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Azure AD</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>AWS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Microsoft 365</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -592,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -603,97 +932,800 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Present?</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Parser / Format</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Normalized (Y/N)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Last Event Seen</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Sysmon</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Sysmon XML</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Windows Event Logs</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CloudTrail</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>CloudTrail JSON</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n"/>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n"/>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
+      <c r="E83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+      <c r="E84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n"/>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n"/>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+      <c r="E88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n"/>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n"/>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+      <c r="E90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n"/>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+      <c r="E91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+      <c r="E93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
+      <c r="E95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+      <c r="E96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+      <c r="B99" s="6" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="n"/>
+      <c r="E99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+      <c r="E100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+      <c r="E102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -706,32 +1738,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Tool</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>CrowdStrike Falcon EDR</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Proofpoint Email Security</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -744,32 +2076,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Asset</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Customer database</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Payment processing service</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
